--- a/automation/reports/Excel/Failed_Test_Cases.xlsx
+++ b/automation/reports/Excel/Failed_Test_Cases.xlsx
@@ -32,7 +32,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -43,6 +43,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -58,11 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -428,12 +434,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
@@ -471,6 +477,5106 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TC_AUTH_001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>test_auth_cases[1]</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>12.315</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC_AUTH_002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>test_auth_cases[2]</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>12.295</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TC_AUTH_003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>test_auth_cases[3]</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TC_AUTH_004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>test_auth_cases[4]</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>12.282</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TC_AUTH_005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>test_auth_cases[5]</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12.284</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TC_AUTH_006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>test_auth_cases[6]</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12.189</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>TC_AUTH_007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>test_auth_cases[7]</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TC_AUTH_008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>test_auth_cases[8]</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>12.372</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>TC_AUTH_009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>test_auth_cases[9]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>TC_AUTH_010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>test_auth_cases[10]</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>12.297</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TC_AUTH_011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>test_auth_cases[11]</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>12.242</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TC_AUTH_012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>test_auth_cases[12]</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>12.311</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TC_AUTH_013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>test_auth_cases[13]</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>12.218</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TC_AUTH_014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>test_auth_cases[14]</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TC_AUTH_015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>test_auth_cases[15]</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>12.27</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TC_AUTH_016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>test_auth_cases[16]</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>12.278</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TC_AUTH_017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>test_auth_cases[17]</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>12.272</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TC_AUTH_018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>test_auth_cases[18]</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>12.227</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TC_AUTH_019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>test_auth_cases[19]</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>12.293</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TC_AUTH_020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>test_auth_cases[20]</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>12.258</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TC_AUTH_021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>test_auth_cases[21]</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>12.211</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TC_AUTH_022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>test_auth_cases[22]</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>12.262</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TC_AUTH_023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>test_auth_cases[23]</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>12.333</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TC_AUTH_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>test_auth_cases[24]</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TC_AUTH_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>test_auth_cases[25]</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>12.281</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TC_AUTH_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>test_auth_cases[26]</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>12.283</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TC_AUTH_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>test_auth_cases[27]</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>12.292</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TC_AUTH_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>test_auth_cases[28]</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TC_AUTH_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>test_auth_cases[29]</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>12.276</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TC_AUTH_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>test_auth_cases[30]</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>12.331</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TC_AUTH_031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>test_auth_cases[31]</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>12.253</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TC_AUTH_032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>test_auth_cases[32]</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>12.251</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TC_AUTH_033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>test_auth_cases[33]</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>12.268</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TC_AUTH_034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>test_auth_cases[34]</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>12.258</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TC_AUTH_035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>test_auth_cases[35]</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>12.292</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TC_AUTH_036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>test_auth_cases[36]</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>12.269</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TC_AUTH_037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>test_auth_cases[37]</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>12.238</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>TC_AUTH_038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>test_auth_cases[38]</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>TC_AUTH_039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>test_auth_cases[39]</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>12.284</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>TC_AUTH_040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Authentication</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>test_auth_cases[40]</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>TC_FORM_001</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>test_form_cases[1]</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>12.338</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>TC_FORM_002</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>test_form_cases[2]</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>12.303</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TC_FORM_003</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>test_form_cases[3]</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>12.256</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TC_FORM_004</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>test_form_cases[4]</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>12.236</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TC_FORM_005</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>test_form_cases[5]</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>12.334</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>TC_FORM_006</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>test_form_cases[6]</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>12.191</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>TC_FORM_007</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>test_form_cases[7]</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>12.234</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>TC_FORM_008</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>test_form_cases[8]</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>12.268</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TC_FORM_009</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>test_form_cases[9]</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>12.303</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TC_FORM_010</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>test_form_cases[10]</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>12.324</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TC_FORM_011</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>test_form_cases[11]</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>12.297</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TC_FORM_012</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>test_form_cases[12]</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TC_FORM_013</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>test_form_cases[13]</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>12.34</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TC_FORM_014</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>test_form_cases[14]</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>12.227</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TC_FORM_015</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>test_form_cases[15]</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>12.271</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TC_FORM_016</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>test_form_cases[16]</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>12.282</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TC_FORM_017</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>test_form_cases[17]</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>12.321</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TC_FORM_018</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>test_form_cases[18]</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TC_FORM_019</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>test_form_cases[19]</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>12.272</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TC_FORM_020</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>test_form_cases[20]</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>12.309</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TC_FORM_021</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>test_form_cases[21]</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TC_FORM_022</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>test_form_cases[22]</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>12.278</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TC_FORM_023</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>test_form_cases[23]</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>12.297</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TC_FORM_024</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>test_form_cases[24]</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>12.282</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TC_FORM_025</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>test_form_cases[25]</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TC_FORM_026</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>test_form_cases[26]</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>12.313</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TC_FORM_027</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>test_form_cases[27]</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>12.277</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TC_FORM_028</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>test_form_cases[28]</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TC_FORM_029</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>test_form_cases[29]</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>12.291</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TC_FORM_030</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>test_form_cases[30]</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>12.301</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TC_FORM_031</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>test_form_cases[31]</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>12.267</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TC_FORM_032</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>test_form_cases[32]</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>12.301</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TC_FORM_033</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>test_form_cases[33]</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TC_FORM_034</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>test_form_cases[34]</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TC_FORM_035</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>test_form_cases[35]</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>12.323</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TC_FORM_036</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>test_form_cases[36]</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>12.303</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TC_FORM_037</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>test_form_cases[37]</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>12.287</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TC_FORM_038</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>test_form_cases[38]</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>12.307</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TC_FORM_039</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>test_form_cases[39]</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>12.289</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TC_FORM_040</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>test_form_cases[40]</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TC_FORM_041</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>test_form_cases[41]</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>12.279</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TC_FORM_042</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>test_form_cases[42]</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TC_FORM_043</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>test_form_cases[43]</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>12.296</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TC_FORM_044</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>test_form_cases[44]</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TC_FORM_045</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>test_form_cases[45]</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>12.292</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TC_FORM_046</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>test_form_cases[46]</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>12.277</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TC_FORM_047</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>test_form_cases[47]</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>12.306</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TC_FORM_048</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>test_form_cases[48]</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>12.298</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TC_FORM_049</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>test_form_cases[49]</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>12.282</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TC_FORM_050</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Forms</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>test_form_cases[50]</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TC_NAV_001</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>test_nav_cases[1]</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>12.318</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TC_NAV_002</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>test_nav_cases[2]</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>12.289</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TC_NAV_003</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>test_nav_cases[3]</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>12.287</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TC_NAV_004</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>test_nav_cases[4]</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>12.288</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TC_NAV_005</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>test_nav_cases[5]</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>12.285</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TC_NAV_006</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>test_nav_cases[6]</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>12.293</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TC_NAV_007</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>test_nav_cases[7]</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>12.306</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TC_NAV_008</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>test_nav_cases[8]</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TC_NAV_009</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>test_nav_cases[9]</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>12.295</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TC_NAV_010</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>test_nav_cases[10]</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>12.303</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TC_NAV_011</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>test_nav_cases[11]</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>12.269</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TC_NAV_012</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>test_nav_cases[12]</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>12.302</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TC_NAV_013</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>test_nav_cases[13]</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>12.304</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TC_NAV_014</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>test_nav_cases[14]</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>12.304</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TC_NAV_015</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>test_nav_cases[15]</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>12.298</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TC_NAV_016</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>test_nav_cases[16]</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>12.301</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TC_NAV_017</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>test_nav_cases[17]</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>12.277</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TC_NAV_018</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>test_nav_cases[18]</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>12.308</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TC_NAV_019</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>test_nav_cases[19]</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>12.299</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TC_NAV_020</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>test_nav_cases[20]</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>12.289</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TC_NAV_021</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>test_nav_cases[21]</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>12.304</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TC_NAV_022</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>test_nav_cases[22]</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TC_NAV_023</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>test_nav_cases[23]</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>12.303</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TC_NAV_024</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>test_nav_cases[24]</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>12.298</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TC_NAV_025</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>test_nav_cases[25]</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>12.315</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TC_NAV_026</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>test_nav_cases[26]</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>12.286</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TC_NAV_027</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>test_nav_cases[27]</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>12.309</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TC_NAV_028</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>test_nav_cases[28]</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>12.301</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TC_NAV_029</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>test_nav_cases[29]</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>12.287</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TC_NAV_030</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>test_nav_cases[30]</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>12.293</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TC_UI_001</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>test_ui_cases[1]</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>4.778</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TC_UI_002</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>test_ui_cases[2]</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>4.743</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>TC_UI_003</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>test_ui_cases[3]</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>4.773</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TC_UI_004</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>test_ui_cases[4]</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TC_UI_005</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>test_ui_cases[5]</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>4.749</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TC_UI_006</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>test_ui_cases[6]</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>4.805</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TC_UI_007</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>test_ui_cases[7]</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4.751</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TC_UI_008</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>test_ui_cases[8]</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>4.769</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TC_UI_009</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>test_ui_cases[9]</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TC_UI_010</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>test_ui_cases[10]</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>4.699</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TC_UI_011</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>test_ui_cases[11]</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TC_UI_012</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>test_ui_cases[12]</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>4.759</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TC_UI_013</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>test_ui_cases[13]</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TC_UI_014</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>test_ui_cases[14]</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>4.747</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TC_UI_015</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>test_ui_cases[15]</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>4.707</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>TC_UI_016</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>test_ui_cases[16]</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>4.681</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>TC_UI_017</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>test_ui_cases[17]</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>4.742</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>TC_UI_018</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>test_ui_cases[18]</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>4.708</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>TC_UI_019</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>test_ui_cases[19]</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>TC_UI_020</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>test_ui_cases[20]</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>4.753</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>TC_UI_021</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>test_ui_cases[21]</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>4.755</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>TC_UI_022</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>test_ui_cases[22]</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>4.701</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>TC_UI_023</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>test_ui_cases[23]</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>4.714</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>TC_UI_024</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>test_ui_cases[24]</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TC_UI_025</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>test_ui_cases[25]</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>4.769</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>TC_UI_026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>test_ui_cases[26]</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>4.783</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>TC_UI_027</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>test_ui_cases[27]</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>TC_UI_028</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>test_ui_cases[28]</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>4.749</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>TC_UI_029</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>test_ui_cases[29]</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>4.687</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>TC_UI_030</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>test_ui_cases[30]</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>4.723</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>TC_UI_031</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>test_ui_cases[31]</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>4.725</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>TC_UI_032</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>test_ui_cases[32]</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>4.776</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>TC_UI_033</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>test_ui_cases[33]</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>4.788</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>TC_UI_034</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>test_ui_cases[34]</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>4.703</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>TC_UI_035</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>test_ui_cases[35]</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>4.729</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>TC_UI_036</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>test_ui_cases[36]</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>4.747</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>TC_UI_037</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>test_ui_cases[37]</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>4.738</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>TC_UI_038</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>test_ui_cases[38]</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>4.766</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>TC_UI_039</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>test_ui_cases[39]</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>4.748</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>TC_UI_040</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>test_ui_cases[40]</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>4.764</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>TC_UI_041</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>test_ui_cases[41]</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>4.767</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>TC_UI_042</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>test_ui_cases[42]</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>4.697</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>TC_UI_043</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>test_ui_cases[43]</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>4.761</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>TC_UI_044</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>test_ui_cases[44]</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>4.724</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>TC_UI_045</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>test_ui_cases[45]</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>4.777</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>TC_UI_046</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>test_ui_cases[46]</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>4.744</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>TC_UI_047</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>test_ui_cases[47]</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>4.721</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>TC_UI_048</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>test_ui_cases[48]</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>TC_UI_049</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>test_ui_cases[49]</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>4.717</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>TC_UI_050</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>UI Validation</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>test_ui_cases[50]</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>4.757</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
